--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99630</v>
+        <v>99636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99630</v>
+        <v>99636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99636</v>
+        <v>99638</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99636</v>
+        <v>99638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99638</v>
+        <v>99639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99638</v>
+        <v>99639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99639</v>
+        <v>99645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99639</v>
+        <v>99645</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99645</v>
+        <v>99649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99645</v>
+        <v>99649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99649</v>
+        <v>99651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99649</v>
+        <v>99651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99651</v>
+        <v>99653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99651</v>
+        <v>99653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99653</v>
+        <v>99666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99653</v>
+        <v>99666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99666</v>
+        <v>99668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99666</v>
+        <v>99668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99668</v>
+        <v>99671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99668</v>
+        <v>99671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99671</v>
+        <v>99681</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99671</v>
+        <v>99681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99681</v>
+        <v>99682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99681</v>
+        <v>99682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99682</v>
+        <v>99687</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99682</v>
+        <v>99687</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99687</v>
+        <v>99690</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99687</v>
+        <v>99690</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99690</v>
+        <v>99696</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99690</v>
+        <v>99696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99696</v>
+        <v>99708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99696</v>
+        <v>99708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99708</v>
+        <v>99709</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99708</v>
+        <v>99709</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26196-2026 artfynd.xlsx
+++ b/artfynd/A 26196-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921975</v>
       </c>
       <c r="B2" t="n">
-        <v>99709</v>
+        <v>99712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921985</v>
       </c>
       <c r="B3" t="n">
-        <v>99709</v>
+        <v>99712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
